--- a/base_datas/media_porte_detalhamento.xlsx
+++ b/base_datas/media_porte_detalhamento.xlsx
@@ -603,133 +603,133 @@
         </is>
       </c>
       <c r="B2">
-        <v>641.355133017211</v>
+        <v>641.1962708404399</v>
       </c>
       <c r="C2">
-        <v>149.1674542973497</v>
+        <v>150.2535368884634</v>
       </c>
       <c r="D2">
-        <v>6449.55562452665</v>
+        <v>6453.295921602979</v>
       </c>
       <c r="E2">
-        <v>345.9756905494411</v>
+        <v>356.1685196314461</v>
       </c>
       <c r="F2">
-        <v>588.8030153479945</v>
+        <v>588.4886617527956</v>
       </c>
       <c r="G2">
-        <v>50.14536401644651</v>
+        <v>50.23059219637559</v>
       </c>
       <c r="H2">
-        <v>17.80077598319937</v>
+        <v>18.0453635328843</v>
       </c>
       <c r="I2">
-        <v>225.1239468787671</v>
+        <v>226.3122060721744</v>
       </c>
       <c r="J2">
-        <v>64.74575855188407</v>
+        <v>64.99376131762357</v>
       </c>
       <c r="K2">
-        <v>2.545594226084234</v>
+        <v>3.426878823966306</v>
       </c>
       <c r="L2">
-        <v>3858.347648087471</v>
+        <v>3859.005980113347</v>
       </c>
       <c r="M2">
-        <v>1495.89553198412</v>
+        <v>1498.349960328685</v>
       </c>
       <c r="N2">
-        <v>1095.31244445506</v>
+        <v>1095.939981160947</v>
       </c>
       <c r="O2">
-        <v>231.615350504633</v>
+        <v>231.7366002703991</v>
       </c>
       <c r="P2">
-        <v>108.6760030592472</v>
+        <v>127.1562184512393</v>
       </c>
       <c r="Q2">
-        <v>2.946798168783711</v>
+        <v>2.87841365216001</v>
       </c>
       <c r="R2">
         <v>26.57264291966604</v>
       </c>
       <c r="S2">
-        <v>60.31796272498978</v>
+        <v>61.36223724944411</v>
       </c>
       <c r="T2">
-        <v>101.2797072423534</v>
+        <v>101.9488768460313</v>
       </c>
       <c r="U2">
-        <v>66.88002430588655</v>
+        <v>67.39672909896306</v>
       </c>
       <c r="V2">
-        <v>229.5514765346402</v>
+        <v>227.9181424585049</v>
       </c>
       <c r="W2">
-        <v>190.3275007169333</v>
+        <v>190.6865940384117</v>
       </c>
       <c r="Z2">
-        <v>7.58650199727195</v>
+        <v>7.536434722354874</v>
       </c>
       <c r="AA2">
-        <v>23.73182637910688</v>
+        <v>23.77147196351092</v>
       </c>
       <c r="AB2">
-        <v>32.93660227450981</v>
+        <v>32.9816886854507</v>
       </c>
       <c r="AC2">
-        <v>2.031782133562702E-16</v>
+        <v>2.505336263725465E-16</v>
       </c>
       <c r="AD2">
-        <v>9.038566487127381</v>
+        <v>8.859088353099079</v>
       </c>
       <c r="AE2">
-        <v>11.30369209689145</v>
+        <v>11.14404056206053</v>
       </c>
       <c r="AF2">
         <v>35.40463198512754</v>
       </c>
       <c r="AG2">
-        <v>6.061112304616553</v>
+        <v>7.247781482094291</v>
       </c>
       <c r="AH2">
-        <v>2247.141470001221</v>
+        <v>2247.032504213511</v>
       </c>
       <c r="AJ2">
-        <v>173.8707650975027</v>
+        <v>172.916929310256</v>
       </c>
       <c r="AK2">
-        <v>663.5359858511503</v>
+        <v>663.5783928958544</v>
       </c>
       <c r="AL2">
-        <v>128.9035362995671</v>
+        <v>129.043670439147</v>
       </c>
       <c r="AM2">
-        <v>526.2298927327635</v>
+        <v>524.0621505200282</v>
       </c>
       <c r="AN2">
-        <v>30.52908636273312</v>
+        <v>30.55038444759092</v>
       </c>
       <c r="AO2">
-        <v>126.4163013688064</v>
+        <v>130.5650249476328</v>
       </c>
       <c r="AP2">
-        <v>1132.323221225155</v>
+        <v>1133.263842894392</v>
       </c>
       <c r="AQ2">
-        <v>127.5119427805369</v>
+        <v>127.6599353199804</v>
       </c>
       <c r="AR2">
-        <v>104.9790533344364</v>
+        <v>105.0532441600535</v>
       </c>
       <c r="AS2">
-        <v>15.94498026155901</v>
+        <v>15.95586095490817</v>
       </c>
       <c r="AT2">
-        <v>60.55100943272583</v>
+        <v>60.55623515466906</v>
       </c>
       <c r="AU2">
-        <v>126.3082256550515</v>
+        <v>128.0014405907221</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -742,49 +742,49 @@
         </is>
       </c>
       <c r="B3">
-        <v>1358.178217291227</v>
+        <v>1347.839814991044</v>
       </c>
       <c r="C3">
-        <v>239.474649922203</v>
+        <v>237.7694950637183</v>
       </c>
       <c r="D3">
-        <v>4347.084449692204</v>
+        <v>4332.140280344792</v>
       </c>
       <c r="E3">
-        <v>586.0103549438049</v>
+        <v>581.2488515501753</v>
       </c>
       <c r="F3">
-        <v>1253.775846563763</v>
+        <v>1243.31699422405</v>
       </c>
       <c r="G3">
-        <v>103.4165531249799</v>
+        <v>102.9756689385665</v>
       </c>
       <c r="H3">
-        <v>4.693566968848419</v>
+        <v>4.615669621474964</v>
       </c>
       <c r="I3">
-        <v>183.6525681116702</v>
+        <v>181.7100276577767</v>
       </c>
       <c r="J3">
-        <v>93.74860548761032</v>
+        <v>94.01669830653091</v>
       </c>
       <c r="K3">
-        <v>0.3092371532374829</v>
+        <v>0.3052725743498232</v>
       </c>
       <c r="L3">
-        <v>2030.887425656508</v>
+        <v>2019.453619237486</v>
       </c>
       <c r="M3">
-        <v>1495.734154255548</v>
+        <v>1483.552484376723</v>
       </c>
       <c r="N3">
-        <v>828.9613592929634</v>
+        <v>829.1341767305832</v>
       </c>
       <c r="O3">
-        <v>311.9937216424929</v>
+        <v>310.173000819978</v>
       </c>
       <c r="P3">
-        <v>190.947379645138</v>
+        <v>189.9558822223047</v>
       </c>
       <c r="Q3">
         <v>0.387531794467433</v>
@@ -793,34 +793,34 @@
         <v>1.907603964804308</v>
       </c>
       <c r="S3">
-        <v>129.6906854154552</v>
+        <v>127.78306058987</v>
       </c>
       <c r="T3">
-        <v>325.2061812920231</v>
+        <v>322.6236756011872</v>
       </c>
       <c r="U3">
-        <v>115.6105262530484</v>
+        <v>115.2130228865538</v>
       </c>
       <c r="V3">
-        <v>541.0212069963408</v>
+        <v>537.5529754795589</v>
       </c>
       <c r="W3">
-        <v>267.8084267820951</v>
+        <v>265.9866237333279</v>
       </c>
       <c r="Z3">
-        <v>15.87341686138365</v>
+        <v>5.97930846737988</v>
       </c>
       <c r="AA3">
-        <v>42.29789612192275</v>
+        <v>42.14011449547749</v>
       </c>
       <c r="AB3">
-        <v>65.73390712060267</v>
+        <v>65.57133683809141</v>
       </c>
       <c r="AC3">
-        <v>-1.781256888914672E-15</v>
+        <v>-1.72419415075536E-15</v>
       </c>
       <c r="AD3">
-        <v>1.178378772147617</v>
+        <v>1.148669729950013</v>
       </c>
       <c r="AE3">
         <v>2.386465140010241</v>
@@ -832,43 +832,43 @@
         <v>0.5293785905511025</v>
       </c>
       <c r="AH3">
-        <v>967.1231410675676</v>
+        <v>958.4904546818209</v>
       </c>
       <c r="AJ3">
-        <v>158.6187451414569</v>
+        <v>156.0227423115036</v>
       </c>
       <c r="AK3">
-        <v>573.2524544216083</v>
+        <v>572.9397094855518</v>
       </c>
       <c r="AL3">
-        <v>86.23443480497994</v>
+        <v>86.38196541275765</v>
       </c>
       <c r="AM3">
-        <v>199.985025930053</v>
+        <v>202.1857027924264</v>
       </c>
       <c r="AN3">
-        <v>14.46430749070402</v>
+        <v>14.53627310842665</v>
       </c>
       <c r="AO3">
-        <v>53.07770475459184</v>
+        <v>44.77711765196362</v>
       </c>
       <c r="AP3">
-        <v>1074.243897251647</v>
+        <v>1064.473204355096</v>
       </c>
       <c r="AQ3">
-        <v>223.780528155867</v>
+        <v>222.7398298543461</v>
       </c>
       <c r="AR3">
-        <v>120.8512758187893</v>
+        <v>120.0430414806975</v>
       </c>
       <c r="AS3">
-        <v>7.833029357521081</v>
+        <v>7.856486578403476</v>
       </c>
       <c r="AT3">
-        <v>24.04645570079388</v>
+        <v>23.92163878116664</v>
       </c>
       <c r="AU3">
-        <v>72.5821621423833</v>
+        <v>71.75787297983609</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -881,133 +881,133 @@
         </is>
       </c>
       <c r="B4">
-        <v>782.0710370890309</v>
+        <v>779.6371310613665</v>
       </c>
       <c r="C4">
-        <v>179.8921049289116</v>
+        <v>178.3067790651419</v>
       </c>
       <c r="D4">
-        <v>5575.483239845395</v>
+        <v>5581.255098976369</v>
       </c>
       <c r="E4">
-        <v>387.1335409423273</v>
+        <v>382.6324128579094</v>
       </c>
       <c r="F4">
-        <v>708.3765379184455</v>
+        <v>708.8116482493188</v>
       </c>
       <c r="G4">
-        <v>69.53641511149135</v>
+        <v>68.93961959905926</v>
       </c>
       <c r="H4">
-        <v>23.68349764612323</v>
+        <v>13.09105987379382</v>
       </c>
       <c r="I4">
-        <v>216.9437462363239</v>
+        <v>214.1521690964821</v>
       </c>
       <c r="J4">
-        <v>75.6109343033897</v>
+        <v>75.72443329540359</v>
       </c>
       <c r="K4">
-        <v>3.578608439804047</v>
+        <v>0.8327902504738285</v>
       </c>
       <c r="L4">
-        <v>3189.56866293319</v>
+        <v>3194.44751905106</v>
       </c>
       <c r="M4">
-        <v>1357.873213362478</v>
+        <v>1357.825549172245</v>
       </c>
       <c r="N4">
-        <v>1029.029864860833</v>
+        <v>1029.96764572505</v>
       </c>
       <c r="O4">
-        <v>253.7864487667663</v>
+        <v>254.4529619541111</v>
       </c>
       <c r="P4">
-        <v>113.9243562679543</v>
+        <v>104.8859352289666</v>
       </c>
       <c r="Q4">
-        <v>2.527933557288459</v>
+        <v>2.492778928755995</v>
       </c>
       <c r="R4">
         <v>8.004472591020871</v>
       </c>
       <c r="S4">
-        <v>66.7396941348407</v>
+        <v>67.08488306450901</v>
       </c>
       <c r="T4">
-        <v>146.9354950362951</v>
+        <v>147.2073394699179</v>
       </c>
       <c r="U4">
-        <v>79.44784458312563</v>
+        <v>79.10458916974106</v>
       </c>
       <c r="V4">
-        <v>282.3763718173377</v>
+        <v>282.3168665136791</v>
       </c>
       <c r="W4">
-        <v>202.5719731694756</v>
+        <v>203.0117035617053</v>
       </c>
       <c r="Z4">
-        <v>3.720695182853818</v>
+        <v>3.715524806896418</v>
       </c>
       <c r="AA4">
-        <v>35.44378061477808</v>
+        <v>34.67594361186453</v>
       </c>
       <c r="AB4">
-        <v>40.8387719287887</v>
+        <v>40.94203746639548</v>
       </c>
       <c r="AC4">
-        <v>-5.34473712707361E-16</v>
+        <v>-2.444021320319474E-16</v>
       </c>
       <c r="AD4">
-        <v>17.90405419186754</v>
+        <v>5.695854305606498</v>
       </c>
       <c r="AE4">
-        <v>7.221226896047424</v>
+        <v>6.637125123184566</v>
       </c>
       <c r="AF4">
-        <v>32.38174782318656</v>
+        <v>33.56359747144448</v>
       </c>
       <c r="AG4">
-        <v>19.64641293477783</v>
+        <v>2.959022728699872</v>
       </c>
       <c r="AH4">
-        <v>1641.63241874457</v>
+        <v>1641.782142755549</v>
       </c>
       <c r="AJ4">
-        <v>202.4100731640795</v>
+        <v>204.4222239370453</v>
       </c>
       <c r="AK4">
-        <v>628.5257793394405</v>
+        <v>628.2145053759369</v>
       </c>
       <c r="AL4">
-        <v>121.1539164371629</v>
+        <v>121.6408080853667</v>
       </c>
       <c r="AM4">
-        <v>512.1970139883547</v>
+        <v>515.6942102694264</v>
       </c>
       <c r="AN4">
-        <v>25.39897126935889</v>
+        <v>25.36712392368259</v>
       </c>
       <c r="AO4">
-        <v>98.77809681491497</v>
+        <v>96.85914770143049</v>
       </c>
       <c r="AP4">
-        <v>1006.87981271626</v>
+        <v>1006.65796893973</v>
       </c>
       <c r="AQ4">
-        <v>148.7135737902597</v>
+        <v>148.4525918997944</v>
       </c>
       <c r="AR4">
-        <v>100.1590995622079</v>
+        <v>100.4517346620791</v>
       </c>
       <c r="AS4">
-        <v>11.59585220062118</v>
+        <v>11.56571580044151</v>
       </c>
       <c r="AT4">
-        <v>39.58463350105061</v>
+        <v>39.42019068041408</v>
       </c>
       <c r="AU4">
-        <v>101.4769074885261</v>
+        <v>101.7275238207551</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         <v>266.1618779170148</v>
       </c>
       <c r="D5">
-        <v>3880.117245428773</v>
+        <v>3880.94683412837</v>
       </c>
       <c r="E5">
         <v>642.5697113154779</v>
@@ -1056,7 +1056,7 @@
         <v>1436.349957008282</v>
       </c>
       <c r="N5">
-        <v>777.103526181621</v>
+        <v>777.9331148812184</v>
       </c>
       <c r="O5">
         <v>339.1861300569439</v>
@@ -1159,49 +1159,49 @@
         </is>
       </c>
       <c r="B6">
-        <v>655.1245160211754</v>
+        <v>657.0060378003369</v>
       </c>
       <c r="C6">
-        <v>152.6399544597918</v>
+        <v>153.1636643208531</v>
       </c>
       <c r="D6">
-        <v>7486.468882972813</v>
+        <v>7502.072038944903</v>
       </c>
       <c r="E6">
-        <v>392.2252068917009</v>
+        <v>392.2086547002605</v>
       </c>
       <c r="F6">
-        <v>602.738713146466</v>
+        <v>604.6502883299279</v>
       </c>
       <c r="G6">
-        <v>50.57100462422067</v>
+        <v>50.56209546221352</v>
       </c>
       <c r="H6">
-        <v>20.86219436456287</v>
+        <v>21.11368468984394</v>
       </c>
       <c r="I6">
-        <v>262.6907070955322</v>
+        <v>263.8338964564422</v>
       </c>
       <c r="J6">
-        <v>64.67121771853994</v>
+        <v>64.6934651213528</v>
       </c>
       <c r="K6">
-        <v>1.601732495660595</v>
+        <v>1.579989520606379</v>
       </c>
       <c r="L6">
-        <v>4350.784243869847</v>
+        <v>4361.155552634481</v>
       </c>
       <c r="M6">
-        <v>2037.038012449112</v>
+        <v>2040.405147848753</v>
       </c>
       <c r="N6">
-        <v>1099.59619158614</v>
+        <v>1101.45275106942</v>
       </c>
       <c r="O6">
-        <v>288.2042390234166</v>
+        <v>288.3721008386748</v>
       </c>
       <c r="P6">
-        <v>77.45819324381939</v>
+        <v>77.37330257057751</v>
       </c>
       <c r="Q6">
         <v>10.83669448517346</v>
@@ -1210,82 +1210,82 @@
         <v>7.944344908621733</v>
       </c>
       <c r="S6">
-        <v>63.66864100565061</v>
+        <v>63.61075788905804</v>
       </c>
       <c r="T6">
-        <v>80.77463686077377</v>
+        <v>80.36927267873821</v>
       </c>
       <c r="U6">
-        <v>91.07927843168318</v>
+        <v>91.5697665705942</v>
       </c>
       <c r="V6">
-        <v>236.9292741116622</v>
+        <v>238.8635984882151</v>
       </c>
       <c r="W6">
-        <v>195.1443871523528</v>
+        <v>195.030092195146</v>
       </c>
       <c r="Z6">
-        <v>4.779190905674689</v>
+        <v>4.741371637212168</v>
       </c>
       <c r="AA6">
-        <v>22.46532191115046</v>
+        <v>22.52077564796835</v>
       </c>
       <c r="AB6">
-        <v>34.55861016476546</v>
+        <v>34.46058946975593</v>
       </c>
       <c r="AC6">
-        <v>6.924594925821906E-16</v>
+        <v>7.17503223591324E-16</v>
       </c>
       <c r="AD6">
-        <v>14.5652959687163</v>
+        <v>14.81524841338363</v>
       </c>
       <c r="AE6">
         <v>22.63233414213729</v>
       </c>
       <c r="AF6">
-        <v>40.83214436530069</v>
+        <v>40.74921193717159</v>
       </c>
       <c r="AG6">
         <v>7.321412876908883</v>
       </c>
       <c r="AH6">
-        <v>2842.818887011155</v>
+        <v>2844.911593079627</v>
       </c>
       <c r="AJ6">
-        <v>189.8783947685966</v>
+        <v>192.9941797584841</v>
       </c>
       <c r="AK6">
-        <v>673.0619068701532</v>
+        <v>675.2839621854307</v>
       </c>
       <c r="AL6">
-        <v>122.1801314291456</v>
+        <v>122.5522762832591</v>
       </c>
       <c r="AM6">
-        <v>370.3258005429651</v>
+        <v>371.5067321031786</v>
       </c>
       <c r="AN6">
-        <v>45.63190787775156</v>
+        <v>46.0335785331749</v>
       </c>
       <c r="AO6">
-        <v>153.1011044779448</v>
+        <v>153.8082756493501</v>
       </c>
       <c r="AP6">
-        <v>1576.905274365517</v>
+        <v>1580.858890196068</v>
       </c>
       <c r="AQ6">
-        <v>150.8406482029782</v>
+        <v>150.7635887466081</v>
       </c>
       <c r="AR6">
-        <v>125.8989403422463</v>
+        <v>125.618907347748</v>
       </c>
       <c r="AS6">
-        <v>20.98241041130479</v>
+        <v>21.07345425088027</v>
       </c>
       <c r="AT6">
-        <v>32.18726626150264</v>
+        <v>32.07211016079705</v>
       </c>
       <c r="AU6">
-        <v>181.1024672429118</v>
+        <v>181.3548864557177</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1301,13 +1301,13 @@
         <v>1085.752846572399</v>
       </c>
       <c r="C7">
-        <v>212.4242494778784</v>
+        <v>212.5202794751642</v>
       </c>
       <c r="D7">
-        <v>4912.714989390211</v>
+        <v>4913.842828473953</v>
       </c>
       <c r="E7">
-        <v>494.5758167975221</v>
+        <v>494.7642768087072</v>
       </c>
       <c r="F7">
         <v>984.3839958675363</v>
@@ -1319,25 +1319,25 @@
         <v>8.395013833534142</v>
       </c>
       <c r="I7">
-        <v>197.5152683136388</v>
+        <v>197.6672778828021</v>
       </c>
       <c r="J7">
         <v>89.60959048298015</v>
       </c>
       <c r="K7">
-        <v>0.4375086713004407</v>
+        <v>0.4375086713004406</v>
       </c>
       <c r="L7">
-        <v>2587.584761962973</v>
+        <v>2588.316138988029</v>
       </c>
       <c r="M7">
-        <v>1398.427650080327</v>
+        <v>1398.824112139013</v>
       </c>
       <c r="N7">
         <v>926.7025773469107</v>
       </c>
       <c r="O7">
-        <v>279.7863807178488</v>
+        <v>279.7854454703742</v>
       </c>
       <c r="P7">
         <v>150.8069691030762</v>
@@ -1349,22 +1349,22 @@
         <v>6.797042889225421</v>
       </c>
       <c r="S7">
-        <v>107.2922988575247</v>
+        <v>107.4816941161844</v>
       </c>
       <c r="T7">
-        <v>249.7668352134913</v>
+        <v>249.6245603288326</v>
       </c>
       <c r="U7">
-        <v>95.74455341344883</v>
+        <v>95.74402207267092</v>
       </c>
       <c r="V7">
-        <v>398.92261732116</v>
+        <v>398.9172380057073</v>
       </c>
       <c r="W7">
-        <v>238.9203875879952</v>
+        <v>239.0685731288845</v>
       </c>
       <c r="Z7">
-        <v>1.356840281743994</v>
+        <v>1.356840281743995</v>
       </c>
       <c r="AA7">
         <v>41.88727034698501</v>
@@ -1388,7 +1388,7 @@
         <v>2.987961533979543</v>
       </c>
       <c r="AH7">
-        <v>1169.914082112326</v>
+        <v>1170.639121147111</v>
       </c>
       <c r="AJ7">
         <v>232.7967954340548</v>
@@ -1406,13 +1406,13 @@
         <v>18.34448102319643</v>
       </c>
       <c r="AO7">
-        <v>78.48771364439908</v>
+        <v>78.49405163467027</v>
       </c>
       <c r="AP7">
-        <v>1016.304594019886</v>
+        <v>1016.646943290225</v>
       </c>
       <c r="AQ7">
-        <v>187.8029363153236</v>
+        <v>187.8570491036703</v>
       </c>
       <c r="AR7">
         <v>115.7115487699696</v>
@@ -1585,49 +1585,49 @@
         </is>
       </c>
       <c r="B9">
-        <v>767.9346267595233</v>
+        <v>766.2199551043088</v>
       </c>
       <c r="C9">
-        <v>210.5585392067447</v>
+        <v>211.995394117308</v>
       </c>
       <c r="D9">
-        <v>11983.96398825761</v>
+        <v>11987.06381478132</v>
       </c>
       <c r="E9">
-        <v>651.6599878211069</v>
+        <v>649.5766404755184</v>
       </c>
       <c r="F9">
-        <v>715.7050314163776</v>
+        <v>714.2827223105833</v>
       </c>
       <c r="G9">
-        <v>50.46506258527391</v>
+        <v>50.21914991495668</v>
       </c>
       <c r="H9">
         <v>22.80098477608593</v>
       </c>
       <c r="I9">
-        <v>418.1970875207778</v>
+        <v>421.7493931048221</v>
       </c>
       <c r="J9">
-        <v>61.53501628698417</v>
+        <v>61.60788829858705</v>
       </c>
       <c r="K9">
-        <v>3.463110527433995</v>
+        <v>3.44880015335369</v>
       </c>
       <c r="L9">
-        <v>7788.933622213286</v>
+        <v>7797.990826543201</v>
       </c>
       <c r="M9">
-        <v>3073.37517811332</v>
+        <v>3064.408597162254</v>
       </c>
       <c r="N9">
-        <v>1123.4455393882</v>
+        <v>1126.442516595349</v>
       </c>
       <c r="O9">
-        <v>518.7389279114377</v>
+        <v>517.449809552033</v>
       </c>
       <c r="P9">
-        <v>101.5392577399149</v>
+        <v>101.4906385578734</v>
       </c>
       <c r="Q9">
         <v>25.30651198097452</v>
@@ -1636,31 +1636,31 @@
         <v>9.027229819320794</v>
       </c>
       <c r="S9">
-        <v>75.14114614404288</v>
+        <v>74.59971775962242</v>
       </c>
       <c r="T9">
-        <v>73.31053198154818</v>
+        <v>73.08569955639908</v>
       </c>
       <c r="U9">
-        <v>117.1931130390689</v>
+        <v>117.9774873224762</v>
       </c>
       <c r="V9">
-        <v>242.1412292353831</v>
+        <v>241.4510950320953</v>
       </c>
       <c r="W9">
-        <v>286.0071070104685</v>
+        <v>285.0046689790807</v>
       </c>
       <c r="Z9">
-        <v>5.129131918243649</v>
+        <v>5.07038525794809</v>
       </c>
       <c r="AA9">
-        <v>21.11436135146404</v>
+        <v>21.07204063107124</v>
       </c>
       <c r="AB9">
-        <v>35.87134139909339</v>
+        <v>35.61860899777894</v>
       </c>
       <c r="AC9">
-        <v>-2.750118031423882E-16</v>
+        <v>-2.731212620186663E-16</v>
       </c>
       <c r="AD9">
         <v>20.0527367317355</v>
@@ -1675,43 +1675,43 @@
         <v>18.3295096855947</v>
       </c>
       <c r="AH9">
-        <v>6241.568123674253</v>
+        <v>6247.876700981588</v>
       </c>
       <c r="AJ9">
-        <v>217.6429997790304</v>
+        <v>216.8744002843455</v>
       </c>
       <c r="AK9">
-        <v>763.2603227345894</v>
+        <v>765.6130227808725</v>
       </c>
       <c r="AL9">
-        <v>122.8815370689273</v>
+        <v>122.7831915897438</v>
       </c>
       <c r="AM9">
-        <v>194.3323147606544</v>
+        <v>194.9148365299632</v>
       </c>
       <c r="AN9">
-        <v>72.44073640272347</v>
+        <v>72.69323240132086</v>
       </c>
       <c r="AO9">
-        <v>222.6702934260946</v>
+        <v>223.3651769745029</v>
       </c>
       <c r="AP9">
-        <v>2415.767453792488</v>
+        <v>2408.544333619571</v>
       </c>
       <c r="AQ9">
-        <v>164.7843804602247</v>
+        <v>164.2344795205242</v>
       </c>
       <c r="AR9">
-        <v>187.7415628715854</v>
+        <v>187.1044035399852</v>
       </c>
       <c r="AS9">
-        <v>39.23078375919189</v>
+        <v>39.14206134892655</v>
       </c>
       <c r="AT9">
-        <v>52.83126191278017</v>
+        <v>52.4560737854535</v>
       </c>
       <c r="AU9">
-        <v>293.7505985056381</v>
+        <v>293.0168241470277</v>
       </c>
       <c r="AV9">
         <v>1</v>

--- a/base_datas/media_porte_detalhamento.xlsx
+++ b/base_datas/media_porte_detalhamento.xlsx
@@ -603,133 +603,133 @@
         </is>
       </c>
       <c r="B2">
-        <v>641.355133017211</v>
+        <v>641.1962708404399</v>
       </c>
       <c r="C2">
-        <v>149.1674542973497</v>
+        <v>150.2535368884634</v>
       </c>
       <c r="D2">
-        <v>6449.55562452665</v>
+        <v>6453.295921602979</v>
       </c>
       <c r="E2">
-        <v>345.9756905494411</v>
+        <v>356.1685196314461</v>
       </c>
       <c r="F2">
-        <v>588.8030153479945</v>
+        <v>588.4886617527956</v>
       </c>
       <c r="G2">
-        <v>50.14536401644651</v>
+        <v>50.23059219637559</v>
       </c>
       <c r="H2">
-        <v>17.80077598319937</v>
+        <v>18.0453635328843</v>
       </c>
       <c r="I2">
-        <v>225.1239468787671</v>
+        <v>226.3122060721744</v>
       </c>
       <c r="J2">
-        <v>64.74575855188407</v>
+        <v>64.99376131762357</v>
       </c>
       <c r="K2">
-        <v>2.545594226084234</v>
+        <v>3.426878823966306</v>
       </c>
       <c r="L2">
-        <v>3858.347648087471</v>
+        <v>3859.005980113347</v>
       </c>
       <c r="M2">
-        <v>1495.89553198412</v>
+        <v>1498.349960328685</v>
       </c>
       <c r="N2">
-        <v>1095.31244445506</v>
+        <v>1095.939981160947</v>
       </c>
       <c r="O2">
-        <v>231.615350504633</v>
+        <v>231.7366002703991</v>
       </c>
       <c r="P2">
-        <v>108.6760030592472</v>
+        <v>127.1562184512393</v>
       </c>
       <c r="Q2">
-        <v>2.946798168783711</v>
+        <v>2.87841365216001</v>
       </c>
       <c r="R2">
         <v>26.57264291966604</v>
       </c>
       <c r="S2">
-        <v>60.31796272498978</v>
+        <v>61.36223724944411</v>
       </c>
       <c r="T2">
-        <v>101.2797072423534</v>
+        <v>101.9488768460313</v>
       </c>
       <c r="U2">
-        <v>66.88002430588655</v>
+        <v>67.39672909896306</v>
       </c>
       <c r="V2">
-        <v>229.5514765346402</v>
+        <v>227.9181424585049</v>
       </c>
       <c r="W2">
-        <v>190.3275007169333</v>
+        <v>190.6865940384117</v>
       </c>
       <c r="Z2">
-        <v>7.58650199727195</v>
+        <v>7.536434722354874</v>
       </c>
       <c r="AA2">
-        <v>23.73182637910688</v>
+        <v>23.77147196351092</v>
       </c>
       <c r="AB2">
-        <v>32.93660227450981</v>
+        <v>32.9816886854507</v>
       </c>
       <c r="AC2">
-        <v>2.031782133562702E-16</v>
+        <v>2.505336263725465E-16</v>
       </c>
       <c r="AD2">
-        <v>9.038566487127381</v>
+        <v>8.859088353099079</v>
       </c>
       <c r="AE2">
-        <v>11.30369209689145</v>
+        <v>11.14404056206053</v>
       </c>
       <c r="AF2">
         <v>35.40463198512754</v>
       </c>
       <c r="AG2">
-        <v>6.061112304616553</v>
+        <v>7.247781482094291</v>
       </c>
       <c r="AH2">
-        <v>2247.141470001221</v>
+        <v>2247.032504213511</v>
       </c>
       <c r="AJ2">
-        <v>173.8707650975027</v>
+        <v>172.916929310256</v>
       </c>
       <c r="AK2">
-        <v>663.5359858511503</v>
+        <v>663.5783928958544</v>
       </c>
       <c r="AL2">
-        <v>128.9035362995671</v>
+        <v>129.043670439147</v>
       </c>
       <c r="AM2">
-        <v>526.2298927327635</v>
+        <v>524.0621505200282</v>
       </c>
       <c r="AN2">
-        <v>30.52908636273312</v>
+        <v>30.55038444759092</v>
       </c>
       <c r="AO2">
-        <v>126.4163013688064</v>
+        <v>130.5650249476328</v>
       </c>
       <c r="AP2">
-        <v>1132.323221225155</v>
+        <v>1133.263842894392</v>
       </c>
       <c r="AQ2">
-        <v>127.5119427805369</v>
+        <v>127.6599353199804</v>
       </c>
       <c r="AR2">
-        <v>104.9790533344364</v>
+        <v>105.0532441600535</v>
       </c>
       <c r="AS2">
-        <v>15.94498026155901</v>
+        <v>15.95586095490817</v>
       </c>
       <c r="AT2">
-        <v>60.55100943272583</v>
+        <v>60.55623515466906</v>
       </c>
       <c r="AU2">
-        <v>126.3082256550515</v>
+        <v>128.0014405907221</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -742,49 +742,49 @@
         </is>
       </c>
       <c r="B3">
-        <v>1358.178217291227</v>
+        <v>1347.839814991044</v>
       </c>
       <c r="C3">
-        <v>239.474649922203</v>
+        <v>237.7694950637183</v>
       </c>
       <c r="D3">
-        <v>4347.084449692204</v>
+        <v>4332.140280344792</v>
       </c>
       <c r="E3">
-        <v>586.0103549438049</v>
+        <v>581.2488515501753</v>
       </c>
       <c r="F3">
-        <v>1253.775846563763</v>
+        <v>1243.31699422405</v>
       </c>
       <c r="G3">
-        <v>103.4165531249799</v>
+        <v>102.9756689385665</v>
       </c>
       <c r="H3">
-        <v>4.693566968848419</v>
+        <v>4.615669621474964</v>
       </c>
       <c r="I3">
-        <v>183.6525681116702</v>
+        <v>181.7100276577767</v>
       </c>
       <c r="J3">
-        <v>93.74860548761032</v>
+        <v>94.01669830653091</v>
       </c>
       <c r="K3">
-        <v>0.3092371532374829</v>
+        <v>0.3052725743498232</v>
       </c>
       <c r="L3">
-        <v>2030.887425656508</v>
+        <v>2019.453619237486</v>
       </c>
       <c r="M3">
-        <v>1495.734154255548</v>
+        <v>1483.552484376723</v>
       </c>
       <c r="N3">
-        <v>828.9613592929634</v>
+        <v>829.1341767305832</v>
       </c>
       <c r="O3">
-        <v>311.9937216424929</v>
+        <v>310.173000819978</v>
       </c>
       <c r="P3">
-        <v>190.947379645138</v>
+        <v>189.9558822223047</v>
       </c>
       <c r="Q3">
         <v>0.387531794467433</v>
@@ -793,34 +793,34 @@
         <v>1.907603964804308</v>
       </c>
       <c r="S3">
-        <v>129.6906854154552</v>
+        <v>127.78306058987</v>
       </c>
       <c r="T3">
-        <v>325.2061812920231</v>
+        <v>322.6236756011872</v>
       </c>
       <c r="U3">
-        <v>115.6105262530484</v>
+        <v>115.2130228865538</v>
       </c>
       <c r="V3">
-        <v>541.0212069963408</v>
+        <v>537.5529754795589</v>
       </c>
       <c r="W3">
-        <v>267.8084267820951</v>
+        <v>265.9866237333279</v>
       </c>
       <c r="Z3">
-        <v>15.87341686138365</v>
+        <v>5.97930846737988</v>
       </c>
       <c r="AA3">
-        <v>42.29789612192275</v>
+        <v>42.14011449547749</v>
       </c>
       <c r="AB3">
-        <v>65.73390712060267</v>
+        <v>65.57133683809141</v>
       </c>
       <c r="AC3">
-        <v>-1.781256888914672E-15</v>
+        <v>-1.72419415075536E-15</v>
       </c>
       <c r="AD3">
-        <v>1.178378772147617</v>
+        <v>1.148669729950013</v>
       </c>
       <c r="AE3">
         <v>2.386465140010241</v>
@@ -832,43 +832,43 @@
         <v>0.5293785905511025</v>
       </c>
       <c r="AH3">
-        <v>967.1231410675676</v>
+        <v>958.4904546818209</v>
       </c>
       <c r="AJ3">
-        <v>158.6187451414569</v>
+        <v>156.0227423115036</v>
       </c>
       <c r="AK3">
-        <v>573.2524544216083</v>
+        <v>572.9397094855518</v>
       </c>
       <c r="AL3">
-        <v>86.23443480497994</v>
+        <v>86.38196541275765</v>
       </c>
       <c r="AM3">
-        <v>199.985025930053</v>
+        <v>202.1857027924264</v>
       </c>
       <c r="AN3">
-        <v>14.46430749070402</v>
+        <v>14.53627310842665</v>
       </c>
       <c r="AO3">
-        <v>53.07770475459184</v>
+        <v>44.77711765196362</v>
       </c>
       <c r="AP3">
-        <v>1074.243897251647</v>
+        <v>1064.473204355096</v>
       </c>
       <c r="AQ3">
-        <v>223.780528155867</v>
+        <v>222.7398298543461</v>
       </c>
       <c r="AR3">
-        <v>120.8512758187893</v>
+        <v>120.0430414806975</v>
       </c>
       <c r="AS3">
-        <v>7.833029357521081</v>
+        <v>7.856486578403476</v>
       </c>
       <c r="AT3">
-        <v>24.04645570079388</v>
+        <v>23.92163878116664</v>
       </c>
       <c r="AU3">
-        <v>72.5821621423833</v>
+        <v>71.75787297983609</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -881,133 +881,133 @@
         </is>
       </c>
       <c r="B4">
-        <v>782.0710370890309</v>
+        <v>779.6371310613665</v>
       </c>
       <c r="C4">
-        <v>179.8921049289116</v>
+        <v>178.3067790651419</v>
       </c>
       <c r="D4">
-        <v>5575.483239845395</v>
+        <v>5581.255098976369</v>
       </c>
       <c r="E4">
-        <v>387.1335409423273</v>
+        <v>382.6324128579094</v>
       </c>
       <c r="F4">
-        <v>708.3765379184455</v>
+        <v>708.8116482493188</v>
       </c>
       <c r="G4">
-        <v>69.53641511149135</v>
+        <v>68.93961959905926</v>
       </c>
       <c r="H4">
-        <v>23.68349764612323</v>
+        <v>13.09105987379382</v>
       </c>
       <c r="I4">
-        <v>216.9437462363239</v>
+        <v>214.1521690964821</v>
       </c>
       <c r="J4">
-        <v>75.6109343033897</v>
+        <v>75.72443329540359</v>
       </c>
       <c r="K4">
-        <v>3.578608439804047</v>
+        <v>0.8327902504738285</v>
       </c>
       <c r="L4">
-        <v>3189.56866293319</v>
+        <v>3194.44751905106</v>
       </c>
       <c r="M4">
-        <v>1357.873213362478</v>
+        <v>1357.825549172245</v>
       </c>
       <c r="N4">
-        <v>1029.029864860833</v>
+        <v>1029.96764572505</v>
       </c>
       <c r="O4">
-        <v>253.7864487667663</v>
+        <v>254.4529619541111</v>
       </c>
       <c r="P4">
-        <v>113.9243562679543</v>
+        <v>104.8859352289666</v>
       </c>
       <c r="Q4">
-        <v>2.527933557288459</v>
+        <v>2.492778928755995</v>
       </c>
       <c r="R4">
         <v>8.004472591020871</v>
       </c>
       <c r="S4">
-        <v>66.7396941348407</v>
+        <v>67.08488306450901</v>
       </c>
       <c r="T4">
-        <v>146.9354950362951</v>
+        <v>147.2073394699179</v>
       </c>
       <c r="U4">
-        <v>79.44784458312563</v>
+        <v>79.10458916974106</v>
       </c>
       <c r="V4">
-        <v>282.3763718173377</v>
+        <v>282.3168665136791</v>
       </c>
       <c r="W4">
-        <v>202.5719731694756</v>
+        <v>203.0117035617053</v>
       </c>
       <c r="Z4">
-        <v>3.720695182853818</v>
+        <v>3.715524806896418</v>
       </c>
       <c r="AA4">
-        <v>35.44378061477808</v>
+        <v>34.67594361186453</v>
       </c>
       <c r="AB4">
-        <v>40.8387719287887</v>
+        <v>40.94203746639548</v>
       </c>
       <c r="AC4">
-        <v>-5.34473712707361E-16</v>
+        <v>-2.444021320319474E-16</v>
       </c>
       <c r="AD4">
-        <v>17.90405419186754</v>
+        <v>5.695854305606498</v>
       </c>
       <c r="AE4">
-        <v>7.221226896047424</v>
+        <v>6.637125123184566</v>
       </c>
       <c r="AF4">
-        <v>32.38174782318656</v>
+        <v>33.56359747144448</v>
       </c>
       <c r="AG4">
-        <v>19.64641293477783</v>
+        <v>2.959022728699872</v>
       </c>
       <c r="AH4">
-        <v>1641.63241874457</v>
+        <v>1641.782142755549</v>
       </c>
       <c r="AJ4">
-        <v>202.4100731640795</v>
+        <v>204.4222239370453</v>
       </c>
       <c r="AK4">
-        <v>628.5257793394405</v>
+        <v>628.2145053759369</v>
       </c>
       <c r="AL4">
-        <v>121.1539164371629</v>
+        <v>121.6408080853667</v>
       </c>
       <c r="AM4">
-        <v>512.1970139883547</v>
+        <v>515.6942102694264</v>
       </c>
       <c r="AN4">
-        <v>25.39897126935889</v>
+        <v>25.36712392368259</v>
       </c>
       <c r="AO4">
-        <v>98.77809681491497</v>
+        <v>96.85914770143049</v>
       </c>
       <c r="AP4">
-        <v>1006.87981271626</v>
+        <v>1006.65796893973</v>
       </c>
       <c r="AQ4">
-        <v>148.7135737902597</v>
+        <v>148.4525918997944</v>
       </c>
       <c r="AR4">
-        <v>100.1590995622079</v>
+        <v>100.4517346620791</v>
       </c>
       <c r="AS4">
-        <v>11.59585220062118</v>
+        <v>11.56571580044151</v>
       </c>
       <c r="AT4">
-        <v>39.58463350105061</v>
+        <v>39.42019068041408</v>
       </c>
       <c r="AU4">
-        <v>101.4769074885261</v>
+        <v>101.7275238207551</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         <v>266.1618779170148</v>
       </c>
       <c r="D5">
-        <v>3880.117245428773</v>
+        <v>3880.94683412837</v>
       </c>
       <c r="E5">
         <v>642.5697113154779</v>
@@ -1056,7 +1056,7 @@
         <v>1436.349957008282</v>
       </c>
       <c r="N5">
-        <v>777.103526181621</v>
+        <v>777.9331148812184</v>
       </c>
       <c r="O5">
         <v>339.1861300569439</v>
@@ -1159,49 +1159,49 @@
         </is>
       </c>
       <c r="B6">
-        <v>655.1245160211754</v>
+        <v>656.5703097169907</v>
       </c>
       <c r="C6">
-        <v>152.6399544597918</v>
+        <v>153.0641798365449</v>
       </c>
       <c r="D6">
-        <v>7486.468882972813</v>
+        <v>7497.023151423798</v>
       </c>
       <c r="E6">
-        <v>392.2252068917009</v>
+        <v>392.088007280903</v>
       </c>
       <c r="F6">
-        <v>602.738713146466</v>
+        <v>604.2509255585937</v>
       </c>
       <c r="G6">
-        <v>50.57100462422067</v>
+        <v>50.52446196241505</v>
       </c>
       <c r="H6">
-        <v>20.86219436456287</v>
+        <v>21.01195229684731</v>
       </c>
       <c r="I6">
-        <v>262.6907070955322</v>
+        <v>263.2228814279218</v>
       </c>
       <c r="J6">
-        <v>64.67121771853994</v>
+        <v>64.63409061277842</v>
       </c>
       <c r="K6">
-        <v>1.601732495660595</v>
+        <v>1.579989520606379</v>
       </c>
       <c r="L6">
-        <v>4350.784243869847</v>
+        <v>4358.22375702589</v>
       </c>
       <c r="M6">
-        <v>2037.038012449112</v>
+        <v>2039.07711789022</v>
       </c>
       <c r="N6">
-        <v>1099.59619158614</v>
+        <v>1100.662210077353</v>
       </c>
       <c r="O6">
-        <v>288.2042390234166</v>
+        <v>288.3362662884384</v>
       </c>
       <c r="P6">
-        <v>77.45819324381939</v>
+        <v>77.24646488564042</v>
       </c>
       <c r="Q6">
         <v>10.83669448517346</v>
@@ -1210,82 +1210,82 @@
         <v>7.944344908621733</v>
       </c>
       <c r="S6">
-        <v>63.66864100565061</v>
+        <v>63.55953649510261</v>
       </c>
       <c r="T6">
-        <v>80.77463686077377</v>
+        <v>80.30755621377585</v>
       </c>
       <c r="U6">
-        <v>91.07927843168318</v>
+        <v>91.50261839251371</v>
       </c>
       <c r="V6">
-        <v>236.9292741116622</v>
+        <v>238.7035886557405</v>
       </c>
       <c r="W6">
-        <v>195.1443871523528</v>
+        <v>194.9151902348425</v>
       </c>
       <c r="Z6">
-        <v>4.779190905674689</v>
+        <v>4.735727147167868</v>
       </c>
       <c r="AA6">
-        <v>22.46532191115046</v>
+        <v>22.50526804403509</v>
       </c>
       <c r="AB6">
-        <v>34.55861016476546</v>
+        <v>34.42695381712721</v>
       </c>
       <c r="AC6">
-        <v>6.924594925821906E-16</v>
+        <v>7.17503223591324E-16</v>
       </c>
       <c r="AD6">
-        <v>14.5652959687163</v>
+        <v>14.68595855338461</v>
       </c>
       <c r="AE6">
         <v>22.63233414213729</v>
       </c>
       <c r="AF6">
-        <v>40.83214436530069</v>
+        <v>40.74921193717159</v>
       </c>
       <c r="AG6">
         <v>7.321412876908883</v>
       </c>
       <c r="AH6">
-        <v>2842.818887011155</v>
+        <v>2843.032604538685</v>
       </c>
       <c r="AJ6">
-        <v>189.8783947685966</v>
+        <v>192.8710534695559</v>
       </c>
       <c r="AK6">
-        <v>673.0619068701532</v>
+        <v>674.8018384893318</v>
       </c>
       <c r="AL6">
-        <v>122.1801314291456</v>
+        <v>122.4562367518074</v>
       </c>
       <c r="AM6">
-        <v>370.3258005429651</v>
+        <v>371.5067321031786</v>
       </c>
       <c r="AN6">
-        <v>45.63190787775156</v>
+        <v>45.99936078707037</v>
       </c>
       <c r="AO6">
-        <v>153.1011044779448</v>
+        <v>153.7681924169532</v>
       </c>
       <c r="AP6">
-        <v>1576.905274365517</v>
+        <v>1579.841426937304</v>
       </c>
       <c r="AQ6">
-        <v>150.8406482029782</v>
+        <v>150.6707640047491</v>
       </c>
       <c r="AR6">
-        <v>125.8989403422463</v>
+        <v>125.5262661613963</v>
       </c>
       <c r="AS6">
-        <v>20.98241041130479</v>
+        <v>21.07345425088027</v>
       </c>
       <c r="AT6">
-        <v>32.18726626150264</v>
+        <v>32.07211016079705</v>
       </c>
       <c r="AU6">
-        <v>181.1024672429118</v>
+        <v>181.2141629152977</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1301,13 +1301,13 @@
         <v>1085.752846572399</v>
       </c>
       <c r="C7">
-        <v>212.4242494778784</v>
+        <v>212.5202794751642</v>
       </c>
       <c r="D7">
-        <v>4912.714989390211</v>
+        <v>4913.842828473953</v>
       </c>
       <c r="E7">
-        <v>494.5758167975221</v>
+        <v>494.7642768087072</v>
       </c>
       <c r="F7">
         <v>984.3839958675363</v>
@@ -1319,25 +1319,25 @@
         <v>8.395013833534142</v>
       </c>
       <c r="I7">
-        <v>197.5152683136388</v>
+        <v>197.6672778828021</v>
       </c>
       <c r="J7">
         <v>89.60959048298015</v>
       </c>
       <c r="K7">
-        <v>0.4375086713004407</v>
+        <v>0.4375086713004406</v>
       </c>
       <c r="L7">
-        <v>2587.584761962973</v>
+        <v>2588.316138988029</v>
       </c>
       <c r="M7">
-        <v>1398.427650080327</v>
+        <v>1398.824112139013</v>
       </c>
       <c r="N7">
         <v>926.7025773469107</v>
       </c>
       <c r="O7">
-        <v>279.7863807178488</v>
+        <v>279.7854454703742</v>
       </c>
       <c r="P7">
         <v>150.8069691030762</v>
@@ -1349,22 +1349,22 @@
         <v>6.797042889225421</v>
       </c>
       <c r="S7">
-        <v>107.2922988575247</v>
+        <v>107.4816941161844</v>
       </c>
       <c r="T7">
-        <v>249.7668352134913</v>
+        <v>249.6245603288326</v>
       </c>
       <c r="U7">
-        <v>95.74455341344883</v>
+        <v>95.74402207267092</v>
       </c>
       <c r="V7">
-        <v>398.92261732116</v>
+        <v>398.9172380057073</v>
       </c>
       <c r="W7">
-        <v>238.9203875879952</v>
+        <v>239.0685731288845</v>
       </c>
       <c r="Z7">
-        <v>1.356840281743994</v>
+        <v>1.356840281743995</v>
       </c>
       <c r="AA7">
         <v>41.88727034698501</v>
@@ -1388,7 +1388,7 @@
         <v>2.987961533979543</v>
       </c>
       <c r="AH7">
-        <v>1169.914082112326</v>
+        <v>1170.639121147111</v>
       </c>
       <c r="AJ7">
         <v>232.7967954340548</v>
@@ -1406,13 +1406,13 @@
         <v>18.34448102319643</v>
       </c>
       <c r="AO7">
-        <v>78.48771364439908</v>
+        <v>78.49405163467027</v>
       </c>
       <c r="AP7">
-        <v>1016.304594019886</v>
+        <v>1016.646943290225</v>
       </c>
       <c r="AQ7">
-        <v>187.8029363153236</v>
+        <v>187.8570491036703</v>
       </c>
       <c r="AR7">
         <v>115.7115487699696</v>
@@ -1585,49 +1585,49 @@
         </is>
       </c>
       <c r="B9">
-        <v>767.9346267595233</v>
+        <v>766.2199551043088</v>
       </c>
       <c r="C9">
-        <v>210.5585392067447</v>
+        <v>211.995394117308</v>
       </c>
       <c r="D9">
-        <v>11983.96398825761</v>
+        <v>11987.06381478132</v>
       </c>
       <c r="E9">
-        <v>651.6599878211069</v>
+        <v>649.5766404755184</v>
       </c>
       <c r="F9">
-        <v>715.7050314163776</v>
+        <v>714.2827223105833</v>
       </c>
       <c r="G9">
-        <v>50.46506258527391</v>
+        <v>50.21914991495668</v>
       </c>
       <c r="H9">
         <v>22.80098477608593</v>
       </c>
       <c r="I9">
-        <v>418.1970875207778</v>
+        <v>421.7493931048221</v>
       </c>
       <c r="J9">
-        <v>61.53501628698417</v>
+        <v>61.60788829858705</v>
       </c>
       <c r="K9">
-        <v>3.463110527433995</v>
+        <v>3.44880015335369</v>
       </c>
       <c r="L9">
-        <v>7788.933622213286</v>
+        <v>7797.990826543201</v>
       </c>
       <c r="M9">
-        <v>3073.37517811332</v>
+        <v>3064.408597162254</v>
       </c>
       <c r="N9">
-        <v>1123.4455393882</v>
+        <v>1126.442516595349</v>
       </c>
       <c r="O9">
-        <v>518.7389279114377</v>
+        <v>517.449809552033</v>
       </c>
       <c r="P9">
-        <v>101.5392577399149</v>
+        <v>101.4906385578734</v>
       </c>
       <c r="Q9">
         <v>25.30651198097452</v>
@@ -1636,31 +1636,31 @@
         <v>9.027229819320794</v>
       </c>
       <c r="S9">
-        <v>75.14114614404288</v>
+        <v>74.59971775962242</v>
       </c>
       <c r="T9">
-        <v>73.31053198154818</v>
+        <v>73.08569955639908</v>
       </c>
       <c r="U9">
-        <v>117.1931130390689</v>
+        <v>117.9774873224762</v>
       </c>
       <c r="V9">
-        <v>242.1412292353831</v>
+        <v>241.4510950320953</v>
       </c>
       <c r="W9">
-        <v>286.0071070104685</v>
+        <v>285.0046689790807</v>
       </c>
       <c r="Z9">
-        <v>5.129131918243649</v>
+        <v>5.07038525794809</v>
       </c>
       <c r="AA9">
-        <v>21.11436135146404</v>
+        <v>21.07204063107124</v>
       </c>
       <c r="AB9">
-        <v>35.87134139909339</v>
+        <v>35.61860899777894</v>
       </c>
       <c r="AC9">
-        <v>-2.750118031423882E-16</v>
+        <v>-2.731212620186663E-16</v>
       </c>
       <c r="AD9">
         <v>20.0527367317355</v>
@@ -1675,43 +1675,43 @@
         <v>18.3295096855947</v>
       </c>
       <c r="AH9">
-        <v>6241.568123674253</v>
+        <v>6247.876700981588</v>
       </c>
       <c r="AJ9">
-        <v>217.6429997790304</v>
+        <v>216.8744002843455</v>
       </c>
       <c r="AK9">
-        <v>763.2603227345894</v>
+        <v>765.6130227808725</v>
       </c>
       <c r="AL9">
-        <v>122.8815370689273</v>
+        <v>122.7831915897438</v>
       </c>
       <c r="AM9">
-        <v>194.3323147606544</v>
+        <v>194.9148365299632</v>
       </c>
       <c r="AN9">
-        <v>72.44073640272347</v>
+        <v>72.69323240132086</v>
       </c>
       <c r="AO9">
-        <v>222.6702934260946</v>
+        <v>223.3651769745029</v>
       </c>
       <c r="AP9">
-        <v>2415.767453792488</v>
+        <v>2408.544333619571</v>
       </c>
       <c r="AQ9">
-        <v>164.7843804602247</v>
+        <v>164.2344795205242</v>
       </c>
       <c r="AR9">
-        <v>187.7415628715854</v>
+        <v>187.1044035399852</v>
       </c>
       <c r="AS9">
-        <v>39.23078375919189</v>
+        <v>39.14206134892655</v>
       </c>
       <c r="AT9">
-        <v>52.83126191278017</v>
+        <v>52.4560737854535</v>
       </c>
       <c r="AU9">
-        <v>293.7505985056381</v>
+        <v>293.0168241470277</v>
       </c>
       <c r="AV9">
         <v>1</v>
